--- a/Unity/Assets/Config/Excel/StoryConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StoryConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -91,7 +91,28 @@
     <t>断桥前的争执</t>
   </si>
   <si>
-    <t xml:space="preserve">描述。。。。 </t>
+    <t>瑞恩问你1+1等于几</t>
+  </si>
+  <si>
+    <t>10021,10022,10023</t>
+  </si>
+  <si>
+    <t>拯救张三</t>
+  </si>
+  <si>
+    <t>张三想要你给他一个大大的拥抱</t>
+  </si>
+  <si>
+    <t>20011,20012,20013</t>
+  </si>
+  <si>
+    <t>和张三吵架</t>
+  </si>
+  <si>
+    <t>张三问你1+1等于几</t>
+  </si>
+  <si>
+    <t>20021,20022,20023</t>
   </si>
 </sst>
 </file>
@@ -11281,7 +11302,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{6477A53F-3816-4A92-8CF1-424912A0BE76}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{18C333F5-CE00-4515-91F2-596206E2E237}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11581,8 +11602,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="17.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="22" style="3" customWidth="1"/>
@@ -11678,6 +11699,37 @@
       <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="E6" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="2">
+        <v>2001</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="2">
+        <v>2002</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
